--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_134_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_134_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>16</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -2119,16 +2119,16 @@
         <v>27</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>13</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>6</v>
@@ -2707,7 +2707,7 @@
         <v>12</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2903,10 +2903,10 @@
         <v>16</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
         <v>7</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3491,16 +3491,16 @@
         <v>36</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>6</v>
@@ -3827,16 +3827,16 @@
         <v>140</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>40</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>1</v>
@@ -4880,10 +4880,10 @@
         <v>33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5272,10 +5272,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>92</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
         <v>19</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_134_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_134_EL.xlsx
@@ -674,10 +674,10 @@
         <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -851,20 +851,20 @@
         <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,14 +1739,14 @@
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2131,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="Y30" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6101,25 +6101,25 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -6600,14 +6600,14 @@
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y47" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA47" t="n">
@@ -6633,25 +6633,25 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
